--- a/2_Formulas_Functions/3_Logical_Functions.xlsx
+++ b/2_Formulas_Functions/3_Logical_Functions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Mac\Home\Developer\_Courses\Excel\Excel_Data_Analytics_Course\2_Formulas_Functions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f943803864469b1e/Documents/GitHub/Excel_Data_Analytics/Excel_project_data_analysis/2_Formulas_Functions/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DACF0C-E6D1-403B-A48D-03B483E33508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-102" yWindow="1488" windowWidth="18372" windowHeight="10296" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_1" sheetId="7" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -1320,32 +1320,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D423364-12D3-4C3A-8A6B-C3645EBFE927}">
   <dimension ref="B1:Q16"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.15625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.68359375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.26171875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.26171875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.578125" style="1" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="11.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="14.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="10.26171875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="9.15625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="10.41796875" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="9.68359375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.15625" style="1"/>
-    <col min="18" max="18" width="14.15625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15625" style="1"/>
+    <col min="1" max="1" width="5.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="11.109375" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.21875" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="14.21875" style="1" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="10.21875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="10.44140625" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.109375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="9.6640625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.109375" style="1"/>
+    <col min="18" max="18" width="14.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G1" s="25"/>
     </row>
-    <row r="2" spans="2:17" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:17" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
@@ -1395,7 +1395,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="Q3" s="32"/>
     </row>
-    <row r="4" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Q4" s="32"/>
     </row>
-    <row r="5" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="Q5" s="32"/>
     </row>
-    <row r="6" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="Q6" s="32"/>
     </row>
-    <row r="7" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="Q7" s="32"/>
     </row>
-    <row r="8" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="8" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="Q8" s="32"/>
     </row>
-    <row r="9" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="9" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="5" t="s">
         <v>6</v>
       </c>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="Q9" s="32"/>
     </row>
-    <row r="10" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="5" t="s">
         <v>7</v>
       </c>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="Q10" s="32"/>
     </row>
-    <row r="11" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="Q11" s="32"/>
     </row>
-    <row r="12" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="8" t="s">
         <v>9</v>
       </c>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="Q12" s="33"/>
     </row>
-    <row r="14" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="14" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="17" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="13" t="s">
         <v>22</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="16" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="15" t="s">
         <v>23</v>
       </c>
@@ -2014,33 +2014,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C913A13C-1EE0-4C25-B641-D7D4D62C7E1E}">
   <dimension ref="B1:Q16"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.15625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.68359375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.41796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.26171875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.578125" style="1" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="11.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="14.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="10.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="9.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="10.41796875" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="9.68359375" style="1" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="9.68359375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.15625" style="1"/>
-    <col min="19" max="19" width="14.15625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.15625" style="1"/>
+    <col min="1" max="1" width="5.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="11.109375" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.21875" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="14.21875" style="1" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="10.21875" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="10.44140625" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.109375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="9.6640625" style="1" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="9.6640625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.109375" style="1"/>
+    <col min="19" max="19" width="14.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G1" s="25"/>
     </row>
-    <row r="2" spans="2:17" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:17" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>Not Met</v>
       </c>
     </row>
-    <row r="5" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
@@ -2276,7 +2276,7 @@
         <v>Not Met</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>Not Met</v>
       </c>
     </row>
-    <row r="8" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="8" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
@@ -2462,7 +2462,7 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="9" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="5" t="s">
         <v>6</v>
       </c>
@@ -2524,7 +2524,7 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="5" t="s">
         <v>7</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="11" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
@@ -2648,7 +2648,7 @@
         <v>Not Met</v>
       </c>
     </row>
-    <row r="12" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="8" t="s">
         <v>9</v>
       </c>
@@ -2710,12 +2710,12 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="14" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="14" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="17" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="13" t="s">
         <v>22</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="16" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="15" t="s">
         <v>23</v>
       </c>
@@ -2739,29 +2739,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B18E6D21-2229-4383-8B9A-431F68FAE08C}">
   <dimension ref="A1:R21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.83984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.15625" customWidth="1"/>
-    <col min="3" max="3" width="21.83984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.15625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.15625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.83984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" customWidth="1"/>
+    <col min="3" max="3" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="68.15625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.9453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.26171875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.41796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.5234375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.3125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.41796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.68359375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.05078125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
         <v>46</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
         <v>56</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -2881,7 +2881,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="27" t="s">
         <v>2</v>
       </c>
@@ -2911,7 +2911,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="27" t="s">
         <v>0</v>
       </c>
@@ -2941,7 +2941,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="27" t="s">
         <v>76</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="27" t="s">
         <v>0</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="27" t="s">
         <v>2</v>
       </c>
@@ -3031,7 +3031,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
         <v>2</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="27" t="s">
         <v>2</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
         <v>2</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="27" t="s">
         <v>0</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
         <v>102</v>
       </c>
@@ -3189,7 +3189,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="27" t="s">
         <v>0</v>
       </c>
@@ -3221,7 +3221,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="27" t="s">
         <v>0</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="27" t="s">
         <v>4</v>
       </c>
@@ -3285,7 +3285,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="27" t="s">
         <v>4</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="27" t="s">
         <v>123</v>
       </c>
@@ -3347,7 +3347,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="s">
         <v>0</v>
       </c>
@@ -3379,7 +3379,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="27" t="s">
         <v>0</v>
       </c>
@@ -3409,7 +3409,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="27" t="s">
         <v>123</v>
       </c>
@@ -3449,29 +3449,29 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4064259-8981-41EE-A951-64D7FCDC9F77}">
   <dimension ref="A1:XFD21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.83984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.41796875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="21.83984375" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="11.15625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="38.15625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="14.578125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="18.578125" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="13.83984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.44140625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="21.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="38.109375" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5546875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="68.15625" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.83984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.15625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.26171875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.26171875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.15625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.26171875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.68359375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.41796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.109375" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
         <v>46</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>85000</v>
       </c>
     </row>
-    <row r="2" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
         <v>56</v>
       </c>
@@ -3595,7 +3595,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="3" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -3659,7 +3659,7 @@
         <v>Salary Low</v>
       </c>
     </row>
-    <row r="4" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A4" s="27" t="s">
         <v>2</v>
       </c>
@@ -3721,7 +3721,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="5" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A5" s="27" t="s">
         <v>0</v>
       </c>
@@ -3783,7 +3783,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="6" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A6" s="27" t="s">
         <v>76</v>
       </c>
@@ -3845,7 +3845,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="7" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A7" s="27" t="s">
         <v>0</v>
       </c>
@@ -3907,7 +3907,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="8" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A8" s="27" t="s">
         <v>2</v>
       </c>
@@ -3969,7 +3969,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="9" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
         <v>2</v>
       </c>
@@ -4033,7 +4033,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="10" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A10" s="27" t="s">
         <v>2</v>
       </c>
@@ -4095,7 +4095,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="11" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
         <v>2</v>
       </c>
@@ -4159,7 +4159,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="12" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A12" s="27" t="s">
         <v>0</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="13" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
         <v>102</v>
       </c>
@@ -4287,7 +4287,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="14" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A14" s="27" t="s">
         <v>0</v>
       </c>
@@ -4351,7 +4351,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="15" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A15" s="27" t="s">
         <v>0</v>
       </c>
@@ -4415,7 +4415,7 @@
         <v>Salary Low</v>
       </c>
     </row>
-    <row r="16" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A16" s="27" t="s">
         <v>4</v>
       </c>
@@ -4479,7 +4479,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="27" t="s">
         <v>4</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="27" t="s">
         <v>123</v>
       </c>
@@ -4605,7 +4605,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="s">
         <v>0</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="27" t="s">
         <v>0</v>
       </c>
@@ -4731,7 +4731,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="27" t="s">
         <v>123</v>
       </c>
@@ -4804,17 +4804,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08EBE098-CD97-45AE-AE7E-86DF2D94E426}">
   <dimension ref="B2:F9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.578125" customWidth="1"/>
-    <col min="2" max="2" width="13.41796875" customWidth="1"/>
-    <col min="3" max="3" width="31.41796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="60.41796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.68359375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5546875" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="3" width="31.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="60.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2" s="26" t="s">
         <v>28</v>
       </c>
@@ -4831,7 +4831,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="e">
         <f>1/0</f>
         <v>#DIV/0!</v>
@@ -4851,7 +4851,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" s="27" t="e">
         <f>A4 + "text"</f>
         <v>#VALUE!</v>
@@ -4871,7 +4871,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" s="12" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -4891,7 +4891,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="12" t="e" cm="1">
         <f t="array" aca="1" ref="B6" ca="1">COUNTT(A3:A9)</f>
         <v>#NAME?</v>
@@ -4911,7 +4911,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="27" t="e">
         <f>VLOOKUP("Value", A1:A10, 2, FALSE)</f>
         <v>#N/A</v>
@@ -4931,7 +4931,7 @@
         <v>This hides #N/A error</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="27" t="e">
         <f>SQRT(-1)</f>
         <v>#NUM!</v>
@@ -4951,7 +4951,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="27" t="e">
         <f>SUM(A1:A10 C1:C10)</f>
         <v>#NULL!</v>
@@ -4979,14 +4979,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B83CC08-3BAC-45FD-A105-07186D54808A}">
   <dimension ref="B1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.83984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.578125" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" s="36" t="s">
         <v>137</v>
       </c>
@@ -5000,7 +5000,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="38" t="b">
         <v>1</v>
       </c>
@@ -5016,7 +5016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="38" t="b">
         <v>1</v>
       </c>
@@ -5032,7 +5032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" s="38" t="b">
         <v>0</v>
       </c>
@@ -5048,7 +5048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="40" t="b">
         <v>0</v>
       </c>
